--- a/Data/Building/MeetingRoomTwo.Temperature.xlsx
+++ b/Data/Building/MeetingRoomTwo.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709235957</v>
+        <v>1711829071</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709262924</v>
+        <v>1711853935</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709263704</v>
+        <v>1711857390</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709264725</v>
+        <v>1711858358</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709268131</v>
+        <v>1711861208</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +642,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709269258</v>
+        <v>1711862198</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +675,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +698,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709272148</v>
+        <v>1711864769</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +712,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +731,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709273206</v>
+        <v>1711870110</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +745,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +768,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709276521</v>
+        <v>1711873353</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +782,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +801,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709277397</v>
+        <v>1711874327</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +815,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +838,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709282172</v>
+        <v>1711902330</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +852,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +871,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709283101</v>
+        <v>1711903304</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +885,11 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +908,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709227709</v>
+        <v>1711911795</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +922,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +941,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709228565</v>
+        <v>1711912632</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +955,11 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +978,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709258618</v>
+        <v>1711922541</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +992,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +1011,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709263512</v>
+        <v>1711923356</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1025,11 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1048,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709268149</v>
+        <v>1711930539</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1062,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1081,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709268964</v>
+        <v>1711931348</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1095,11 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1118,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709310623</v>
+        <v>1711933443</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1132,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1151,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709311486</v>
+        <v>1711934408</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1165,11 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1188,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709342172</v>
+        <v>1711937528</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1202,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1221,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709344026</v>
+        <v>1711938492</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1235,11 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1258,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709348855</v>
+        <v>1711940853</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1272,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709349804</v>
+        <v>1711941809</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1305,11 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1328,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709353248</v>
+        <v>1711943363</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1342,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1361,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709357839</v>
+        <v>1711945776</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1375,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1394,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709400452</v>
+        <v>1711947511</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1408,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709409761</v>
+        <v>1711948413</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1441,11 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1464,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709427869</v>
+        <v>1711989499</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1478,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1497,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709434405</v>
+        <v>1711990271</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1511,11 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1534,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709437590</v>
+        <v>1712021768</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1548,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1567,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709438508</v>
+        <v>1712032528</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1577,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1600,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709441603</v>
+        <v>1712035366</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1614,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1633,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709506545</v>
+        <v>1712036098</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1647,11 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1670,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709518045</v>
+        <v>1712040850</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1684,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1703,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709519033</v>
+        <v>1712041684</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1717,11 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1740,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709524180</v>
+        <v>1712105558</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1754,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1773,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709525047</v>
+        <v>1712106431</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1783,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1806,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709528825</v>
+        <v>1712119762</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1816,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Cold</t>
+          <t>MeetingRoomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1839,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709584536</v>
+        <v>1712122840</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1849,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1872,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709602257</v>
+        <v>1712123244</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1886,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1905,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709609499</v>
+        <v>1712124070</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1919,11 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1942,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709612858</v>
+        <v>1712128291</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1956,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1975,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709613817</v>
+        <v>1712129192</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1989,11 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +2012,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709617178</v>
+        <v>1712163849</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +2026,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2045,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709620612</v>
+        <v>1712164614</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2059,11 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2082,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709655877</v>
+        <v>1712190461</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2096,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2115,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709656756</v>
+        <v>1712197541</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2129,11 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2152,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709689025</v>
+        <v>1712200930</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2166,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2185,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709689959</v>
+        <v>1712201881</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2199,11 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2222,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709695140</v>
+        <v>1712204997</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2236,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2255,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709696089</v>
+        <v>1712209643</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2269,11 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2292,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709699797</v>
+        <v>1712214542</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2306,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2325,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709700839</v>
+        <v>1712215400</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2339,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2362,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709704261</v>
+        <v>1712275631</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2376,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2395,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709705277</v>
+        <v>1712276513</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2409,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2432,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709708699</v>
+        <v>1712281422</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2446,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2465,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709709730</v>
+        <v>1712282582</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2479,11 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2502,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709714818</v>
+        <v>1712287652</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2516,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2535,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709715732</v>
+        <v>1712288540</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2549,11 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2572,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709744506</v>
+        <v>1712290593</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2586,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2605,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709745320</v>
+        <v>1712353463</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2619,11 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2642,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709778746</v>
+        <v>1712367891</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2656,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2675,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709779680</v>
+        <v>1712376362</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2685,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2708,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709784724</v>
+        <v>1712385645</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2718,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Cold</t>
+          <t>MeetingRoomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2741,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709785576</v>
+        <v>1712398594</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2751,11 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2774,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709790698</v>
+        <v>1712425829</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2788,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2807,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709791598</v>
+        <v>1712435188</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2821,11 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2844,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709796684</v>
+        <v>1712456200</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2858,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2877,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709797583</v>
+        <v>1712464276</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2887,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2910,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709853970</v>
+        <v>1712473586</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2737,10 +2920,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Cold</t>
+          <t>MeetingRoomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2943,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709854858</v>
+        <v>1712485870</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2953,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2976,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709860316</v>
+        <v>1712512453</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2990,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +3009,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709861223</v>
+        <v>1712521628</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +3023,11 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3046,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709865303</v>
+        <v>1712538974</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3060,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3079,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709866298</v>
+        <v>1712539867</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3093,11 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3116,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709869391</v>
+        <v>1712544501</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3130,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3149,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709877784</v>
+        <v>1712545833</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3159,15 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3186,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709919494</v>
+        <v>1712548937</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3200,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3219,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709928896</v>
+        <v>1712556321</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3229,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3252,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709946413</v>
+        <v>1712597300</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3266,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3285,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709953200</v>
+        <v>1712606391</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3295,15 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3322,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710009587</v>
+        <v>1712624940</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3336,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3355,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710019332</v>
+        <v>1712631619</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3369,11 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3392,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710035406</v>
+        <v>1712634750</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3406,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3425,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710040853</v>
+        <v>1712635582</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3439,11 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3462,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710044250</v>
+        <v>1712637449</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3476,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3495,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710045295</v>
+        <v>1712643957</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3505,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3528,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710048483</v>
+        <v>1712685616</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3542,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3561,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710055276</v>
+        <v>1712697358</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3571,15 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3598,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710092639</v>
+        <v>1712716933</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3612,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3631,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710102096</v>
+        <v>1712717782</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3645,11 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3668,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710122151</v>
+        <v>1712722313</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3682,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3701,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710125504</v>
+        <v>1712723271</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3715,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3738,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710129384</v>
+        <v>1712725515</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3752,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3771,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710130414</v>
+        <v>1712786709</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3785,11 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3808,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710133692</v>
+        <v>1712799544</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3822,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3841,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710136204</v>
+        <v>1712802944</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3601,10 +3851,11 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3874,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710140446</v>
+        <v>1712808773</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3633,10 +3884,11 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Cold</t>
+          <t>MeetingRoomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3907,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710141335</v>
+        <v>1712810225</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3917,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3940,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710174776</v>
+        <v>1712810562</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3954,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3973,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710175568</v>
+        <v>1712871931</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3987,11 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +4010,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710206555</v>
+        <v>1712884564</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +4024,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +4043,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710212318</v>
+        <v>1712885539</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +4057,11 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4080,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710215652</v>
+        <v>1712890161</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4094,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4113,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710216696</v>
+        <v>1712893176</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4127,11 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4150,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710220063</v>
+        <v>1712896221</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4164,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4183,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710278554</v>
+        <v>1712897567</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4197,11 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4220,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710293607</v>
+        <v>1712900832</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4234,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4253,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710301794</v>
+        <v>1712901655</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4263,15 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4290,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710311058</v>
+        <v>1712937616</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4300,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Warm</t>
+          <t>MeetingRoomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4323,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710323426</v>
+        <v>1712938388</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4333,15 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4360,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710353689</v>
+        <v>1712970782</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4374,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4393,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710362881</v>
+        <v>1712971657</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4407,11 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4430,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710386482</v>
+        <v>1712976342</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4444,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4463,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710395940</v>
+        <v>1712977262</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4177,10 +4473,15 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4500,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710437711</v>
+        <v>1712981035</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4514,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4533,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710446858</v>
+        <v>1712981959</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4547,11 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4570,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710466102</v>
+        <v>1712985055</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4584,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4603,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710467571</v>
+        <v>1712986048</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4617,11 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4640,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710471554</v>
+        <v>1712989143</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4654,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4673,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710472558</v>
+        <v>1712990069</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4687,11 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4710,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710475786</v>
+        <v>1712994248</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4724,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4743,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710479945</v>
+        <v>1712995178</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4433,10 +4753,15 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4780,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710524151</v>
+        <v>1713024287</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4794,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4813,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710532062</v>
+        <v>1713025115</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4827,11 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4850,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710554753</v>
+        <v>1713058275</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4864,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4883,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710555627</v>
+        <v>1713059161</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4897,11 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4920,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710558983</v>
+        <v>1713063915</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4934,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4953,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710559985</v>
+        <v>1713064821</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4967,11 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4990,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710563126</v>
+        <v>1713069133</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +5004,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +5023,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710564188</v>
+        <v>1713070122</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +5037,11 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +5060,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710568351</v>
+        <v>1713073338</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +5074,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +5093,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710622799</v>
+        <v>1713074338</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +5107,11 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5130,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710640174</v>
+        <v>1713077529</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +5144,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5163,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710645519</v>
+        <v>1713078587</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5177,11 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5200,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710648951</v>
+        <v>1713082665</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5214,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5233,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710649967</v>
+        <v>1713083578</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5247,11 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5270,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710653065</v>
+        <v>1713110492</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5284,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5303,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710653998</v>
+        <v>1713111330</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5317,11 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5340,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710659051</v>
+        <v>1713142690</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5354,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5373,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710659988</v>
+        <v>1713149657</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5387,11 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5410,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710722446</v>
+        <v>1713153109</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5424,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5443,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710723362</v>
+        <v>1713154053</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5457,11 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5480,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710728224</v>
+        <v>1713158796</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5494,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5513,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710729589</v>
+        <v>1713159628</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5527,11 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5550,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710732964</v>
+        <v>1713225837</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5564,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5583,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710733986</v>
+        <v>1713226761</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5597,11 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5620,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710737322</v>
+        <v>1713230028</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5634,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5653,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710796519</v>
+        <v>1713234776</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5667,11 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5690,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710811968</v>
+        <v>1713237936</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5704,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5723,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710819283</v>
+        <v>1713238946</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5733,15 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5760,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710880094</v>
+        <v>1713241969</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5774,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5793,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710895809</v>
+        <v>1713304141</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5393,10 +5803,15 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5830,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710901119</v>
+        <v>1713315074</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5840,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Warm</t>
+          <t>MeetingRoomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5863,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710910779</v>
+        <v>1713320758</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5873,15 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5900,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710929286</v>
+        <v>1713323841</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5489,10 +5910,11 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Warm</t>
+          <t>MeetingRoomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5933,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710957362</v>
+        <v>1713324552</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5521,10 +5943,15 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5970,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710966809</v>
+        <v>1713326145</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5984,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +6003,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710986855</v>
+        <v>1713327701</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +6017,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +6036,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710995458</v>
+        <v>1713371861</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +6046,11 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Warm</t>
+          <t>MeetingRoomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +6069,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1711005083</v>
+        <v>1713382036</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +6079,15 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +6106,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711016579</v>
+        <v>1713407084</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5681,10 +6116,11 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Warm</t>
+          <t>MeetingRoomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +6139,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1711045633</v>
+        <v>1713407886</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5713,10 +6149,15 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +6176,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1711055299</v>
+        <v>1713410886</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +6190,7 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6209,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711071667</v>
+        <v>1713475210</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +6223,11 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6246,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711075323</v>
+        <v>1713488693</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6260,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6279,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711076196</v>
+        <v>1713495877</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6293,11 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6316,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711079568</v>
+        <v>1713498698</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6330,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6349,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711080591</v>
+        <v>1713501267</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5905,10 +6359,11 @@
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6382,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711083644</v>
+        <v>1713548628</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6396,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6415,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711088182</v>
+        <v>1713558172</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5969,10 +6425,15 @@
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6452,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711138799</v>
+        <v>1713576977</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6466,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6485,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711159608</v>
+        <v>1713584344</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6033,10 +6495,11 @@
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6518,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711162571</v>
+        <v>1713639030</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6532,7 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6551,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711163614</v>
+        <v>1713648420</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6565,11 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6588,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711166082</v>
+        <v>1713662985</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6602,7 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6621,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711167232</v>
+        <v>1713671112</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6631,11 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6654,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711169522</v>
+        <v>1713716945</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6668,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6687,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711172465</v>
+        <v>1713726342</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6701,11 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6724,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1711175826</v>
+        <v>1713746271</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6738,7 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6757,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1711176811</v>
+        <v>1713752268</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6771,11 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6794,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1711180392</v>
+        <v>1713754950</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6808,7 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6827,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1711181305</v>
+        <v>1713759705</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6353,10 +6837,11 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6860,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1711215026</v>
+        <v>1713810043</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6874,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6893,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1711215841</v>
+        <v>1713819067</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6421,6 +6907,11 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6930,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1711225852</v>
+        <v>1713837533</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6453,6 +6944,7 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6963,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711226711</v>
+        <v>1713846434</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6481,10 +6973,11 @@
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6996,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711236434</v>
+        <v>1713847517</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6513,10 +7006,11 @@
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Cold</t>
+          <t>MeetingRoomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +7029,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711237309</v>
+        <v>1713890389</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6545,10 +7039,11 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +7062,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711241340</v>
+        <v>1713895754</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +7076,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +7095,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711247659</v>
+        <v>1713904776</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6613,6 +7109,11 @@
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +7132,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711251053</v>
+        <v>1713918347</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6645,6 +7146,7 @@
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +7165,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711252056</v>
+        <v>1713918608</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6673,10 +7175,11 @@
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +7198,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711255248</v>
+        <v>1713919099</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6709,6 +7212,7 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +7231,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711261526</v>
+        <v>1713922164</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6737,10 +7241,15 @@
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7268,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711302584</v>
+        <v>1713926860</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +7282,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7301,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711312238</v>
+        <v>1713927734</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6805,6 +7315,11 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7338,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711329842</v>
+        <v>1713930837</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7352,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7371,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711335705</v>
+        <v>1713931987</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6869,6 +7385,11 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7408,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711338907</v>
+        <v>1713933343</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6901,6 +7422,7 @@
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7441,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711343060</v>
+        <v>1713936651</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6929,10 +7451,15 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7478,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711388701</v>
+        <v>1713941464</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7492,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7511,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711398331</v>
+        <v>1713942274</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6997,6 +7525,11 @@
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7548,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711416627</v>
+        <v>1714002546</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7029,6 +7562,7 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7581,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711419785</v>
+        <v>1714003195</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7061,6 +7595,11 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7618,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711423733</v>
+        <v>1714007904</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7632,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7651,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711424708</v>
+        <v>1714010031</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7125,6 +7665,11 @@
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7688,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711427928</v>
+        <v>1714014558</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7157,6 +7702,7 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7721,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711428869</v>
+        <v>1714019068</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7189,6 +7735,11 @@
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7758,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1711430478</v>
+        <v>1714066117</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7772,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7791,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1711434041</v>
+        <v>1714066960</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7249,10 +7801,15 @@
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7828,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1711474753</v>
+        <v>1714089642</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7285,6 +7842,7 @@
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7861,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1711479443</v>
+        <v>1714089882</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7313,10 +7871,11 @@
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7894,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1711505685</v>
+        <v>1714093974</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7908,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7927,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1711514928</v>
+        <v>1714100087</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7381,6 +7941,7 @@
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7960,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1711524071</v>
+        <v>1714153237</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7409,10 +7970,11 @@
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Warm</t>
+          <t>MeetingRoomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7993,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1711555957</v>
+        <v>1714162690</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7441,10 +8003,15 @@
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +8030,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1711562706</v>
+        <v>1714181616</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7477,6 +8044,7 @@
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +8063,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1711567900</v>
+        <v>1714188915</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7505,10 +8073,11 @@
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +8096,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1711592607</v>
+        <v>1714198217</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7537,10 +8106,11 @@
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Cold</t>
+          <t>MeetingRoomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +8129,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1711601977</v>
+        <v>1714233796</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7573,6 +8143,7 @@
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +8162,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1711611154</v>
+        <v>1714240133</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7601,10 +8172,11 @@
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Temperature.state: Warm</t>
+          <t>MeetingRoomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +8195,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1711621679</v>
+        <v>1714249496</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7633,10 +8205,147 @@
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
+          <t>MeetingRoomTwo.Temperature.state: ExcessivelyCold</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1714267805</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1714275628</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
           <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1714284994</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1714292865</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
